--- a/TablaMorbilidad_Subsectores.xlsx
+++ b/TablaMorbilidad_Subsectores.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Downloads\TABLERO_STREAMLIT_DASHBOARD\DASHBOARD_Morbilidad_DESPLIEGUE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Downloads\TABLERO_STREAMLIT_DASHBOARD\DASHBOARD_Morbilidad_DESPLIEGUE_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECEACB8-392D-4D14-92CE-7CB3561D2544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39DA9BA-4CCA-4E7A-9645-E8E995B7930B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3F5E094F-8F70-430D-B0BA-DB553EE45739}"/>
   </bookViews>
@@ -573,7 +573,7 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" customWidth="1"/>
     <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -671,8 +671,7 @@
         <v>1250.0676999999962</v>
       </c>
       <c r="E7">
-        <f>(C7/D7)</f>
-        <v>3.959596617847184</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -689,8 +688,7 @@
         <v>735.60400000000232</v>
       </c>
       <c r="E8">
-        <f t="shared" ref="E8:E58" si="0">(C8/D8)</f>
-        <v>2.3491125456087687</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -707,8 +705,7 @@
         <v>2260.9653999999937</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
-        <v>6.4406176056476001</v>
+        <v>64.41</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -725,8 +722,7 @@
         <v>2662.7846999999761</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
-        <v>7.3998243154995524</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -743,8 +739,7 @@
         <v>902.97770000000105</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
-        <v>2.3985187186793198</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -761,8 +756,7 @@
         <v>2901.2899999999909</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
-        <v>3.9086311792340629</v>
+        <v>39.090000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -779,8 +773,7 @@
         <v>2704.3394999999923</v>
       </c>
       <c r="E13">
-        <f t="shared" si="0"/>
-        <v>3.9779515704296831</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -797,8 +790,7 @@
         <v>4655.2753999999968</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
-        <v>12.11525105066827</v>
+        <v>121.15</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -815,8 +807,7 @@
         <v>1699.9487999999963</v>
       </c>
       <c r="E15">
-        <f t="shared" si="0"/>
-        <v>3.3425196994168349</v>
+        <v>33.43</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -833,8 +824,7 @@
         <v>3917.0709000000252</v>
       </c>
       <c r="E16">
-        <f t="shared" si="0"/>
-        <v>11.858873822018316</v>
+        <v>118.59</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -851,8 +841,7 @@
         <v>4828.147199999963</v>
       </c>
       <c r="E17">
-        <f t="shared" si="0"/>
-        <v>7.7446008932785322</v>
+        <v>77.45</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -869,8 +858,7 @@
         <v>2864.3186000000069</v>
       </c>
       <c r="E18">
-        <f t="shared" si="0"/>
-        <v>5.4273856347544633</v>
+        <v>54.27</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -887,8 +875,7 @@
         <v>5098.2465999999858</v>
       </c>
       <c r="E19">
-        <f t="shared" si="0"/>
-        <v>16.418577047450007</v>
+        <v>164.19</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -905,8 +892,7 @@
         <v>3631.7988999999902</v>
       </c>
       <c r="E20">
-        <f t="shared" si="0"/>
-        <v>4.3714280374940637</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -923,8 +909,7 @@
         <v>1827.2416999999959</v>
       </c>
       <c r="E21">
-        <f t="shared" si="0"/>
-        <v>2.1537588305914905</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -941,8 +926,7 @@
         <v>3189.3510999999967</v>
       </c>
       <c r="E22">
-        <f t="shared" si="0"/>
-        <v>2.8425890783865171</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -959,8 +943,7 @@
         <v>3651.3966999999907</v>
       </c>
       <c r="E23">
-        <f t="shared" si="0"/>
-        <v>4.9115306614041563</v>
+        <v>49.12</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -977,8 +960,7 @@
         <v>649.83770000000015</v>
       </c>
       <c r="E24">
-        <f t="shared" si="0"/>
-        <v>2.0496129079614818</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -995,8 +977,7 @@
         <v>4518.6741999999986</v>
       </c>
       <c r="E25">
-        <f t="shared" si="0"/>
-        <v>3.8984884196785101</v>
+        <v>38.979999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1013,8 +994,7 @@
         <v>3553.5849999999946</v>
       </c>
       <c r="E26">
-        <f t="shared" si="0"/>
-        <v>3.062831351438061</v>
+        <v>30.63</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1031,8 +1011,7 @@
         <v>6374.6397999999508</v>
       </c>
       <c r="E27">
-        <f t="shared" si="0"/>
-        <v>13.108537491169365</v>
+        <v>131.09</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1049,8 +1028,7 @@
         <v>2146.8174999999987</v>
       </c>
       <c r="E28">
-        <f t="shared" si="0"/>
-        <v>1.8808950090075192</v>
+        <v>18.809999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1067,8 +1045,7 @@
         <v>6117.343899999998</v>
       </c>
       <c r="E29">
-        <f t="shared" si="0"/>
-        <v>9.9259353769534115</v>
+        <v>99.26</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1085,8 +1062,7 @@
         <v>7380.0190999999631</v>
       </c>
       <c r="E30">
-        <f t="shared" si="0"/>
-        <v>5.8317431625617511</v>
+        <v>58.32</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1103,8 +1079,7 @@
         <v>4007.4281999999771</v>
       </c>
       <c r="E31">
-        <f t="shared" si="0"/>
-        <v>3.8749261229434224</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1121,8 +1096,7 @@
         <v>7850.3179999999675</v>
       </c>
       <c r="E32">
-        <f t="shared" si="0"/>
-        <v>13.052793716636733</v>
+        <v>130.53</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1139,8 +1113,7 @@
         <v>14128.525100000041</v>
       </c>
       <c r="E33">
-        <f t="shared" si="0"/>
-        <v>1.9048813885746383</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1157,8 +1130,7 @@
         <v>12999.45489999995</v>
       </c>
       <c r="E34">
-        <f t="shared" si="0"/>
-        <v>0.63808334547935508</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1175,8 +1147,7 @@
         <v>18185.669599999979</v>
       </c>
       <c r="E35">
-        <f t="shared" si="0"/>
-        <v>2.9381860065246497</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1193,8 +1164,7 @@
         <v>19261.161199999857</v>
       </c>
       <c r="E36">
-        <f t="shared" si="0"/>
-        <v>4.639199584965894</v>
+        <v>46.39</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1211,8 +1181,7 @@
         <v>7361.3686999999663</v>
       </c>
       <c r="E37">
-        <f t="shared" si="0"/>
-        <v>0.64205376888675791</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1229,8 +1198,7 @@
         <v>25127.897699999445</v>
       </c>
       <c r="E38">
-        <f t="shared" si="0"/>
-        <v>2.9012537638993066</v>
+        <v>29.01</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1247,8 +1215,7 @@
         <v>20383.673699999908</v>
       </c>
       <c r="E39">
-        <f t="shared" si="0"/>
-        <v>1.9925384612588504</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1265,8 +1232,7 @@
         <v>26748.365799999512</v>
       </c>
       <c r="E40">
-        <f t="shared" si="0"/>
-        <v>8.342753577790651</v>
+        <v>83.43</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1283,8 +1249,7 @@
         <v>17064.418199999989</v>
       </c>
       <c r="E41">
-        <f t="shared" si="0"/>
-        <v>1.1550625312851213</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1301,8 +1266,7 @@
         <v>28610.576299999753</v>
       </c>
       <c r="E42">
-        <f t="shared" si="0"/>
-        <v>5.3920014707288662</v>
+        <v>53.92</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1319,8 +1283,7 @@
         <v>31342.653199999288</v>
       </c>
       <c r="E43">
-        <f t="shared" si="0"/>
-        <v>3.2997812477152628</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1337,8 +1300,7 @@
         <v>20904.569099999891</v>
       </c>
       <c r="E44">
-        <f t="shared" si="0"/>
-        <v>3.8249872879226912</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1355,8 +1317,7 @@
         <v>35892.676399999385</v>
       </c>
       <c r="E45">
-        <f t="shared" si="0"/>
-        <v>9.7875008487525452</v>
+        <v>97.88</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1373,8 +1334,7 @@
         <v>63.11810000000002</v>
       </c>
       <c r="E46">
-        <f t="shared" si="0"/>
-        <v>4.2777561586929878</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1391,8 +1351,7 @@
         <v>46.441199999999988</v>
       </c>
       <c r="E47">
-        <f t="shared" si="0"/>
-        <v>2.4544396570286731</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1409,8 +1368,7 @@
         <v>191.92730000000006</v>
       </c>
       <c r="E48">
-        <f t="shared" si="0"/>
-        <v>5.4083530847357322</v>
+        <v>54.08</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1427,8 +1385,7 @@
         <v>250.73500000000024</v>
       </c>
       <c r="E49">
-        <f t="shared" si="0"/>
-        <v>8.3994285640217718</v>
+        <v>83.99</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1445,8 +1402,7 @@
         <v>21.597899999999996</v>
       </c>
       <c r="E50">
-        <f t="shared" si="0"/>
-        <v>5.5559511341380432</v>
+        <v>55.56</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1463,8 +1419,7 @@
         <v>310.02700000000038</v>
       </c>
       <c r="E51">
-        <f t="shared" si="0"/>
-        <v>4.4899643837472212</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1481,8 +1436,7 @@
         <v>206.53430000000034</v>
       </c>
       <c r="E52">
-        <f t="shared" si="0"/>
-        <v>5.7521147383267417</v>
+        <v>57.52</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1499,8 +1453,7 @@
         <v>526.02520000000095</v>
       </c>
       <c r="E53">
-        <f t="shared" si="0"/>
-        <v>9.0566720928959032</v>
+        <v>90.57</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1517,8 +1470,7 @@
         <v>145.49510000000009</v>
       </c>
       <c r="E54">
-        <f t="shared" si="0"/>
-        <v>6.6803280179195035</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1535,8 +1487,7 @@
         <v>374.46700000000044</v>
       </c>
       <c r="E55">
-        <f t="shared" si="0"/>
-        <v>4.6144101749953981</v>
+        <v>46.14</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1553,8 +1504,7 @@
         <v>427.40630000000021</v>
       </c>
       <c r="E56">
-        <f t="shared" si="0"/>
-        <v>6.5557806447869398</v>
+        <v>65.56</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1571,8 +1521,7 @@
         <v>218.12870000000026</v>
       </c>
       <c r="E57">
-        <f t="shared" si="0"/>
-        <v>3.9882898719884095</v>
+        <v>39.880000000000003</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1589,8 +1538,7 @@
         <v>787.51629999999716</v>
       </c>
       <c r="E58">
-        <f t="shared" si="0"/>
-        <v>13.18835843524767</v>
+        <v>131.88</v>
       </c>
     </row>
   </sheetData>
